--- a/_Master_Data/item_master.xlsx
+++ b/_Master_Data/item_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NSU_2027\Desktop\미국 공급망 고도화\1. 미국 주재원\비전2030(2026)\4.3.2 수요계획 강화\S&amp;OP\DashBoard 개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF22123-8CF9-43C3-843C-A5E9ADC3DB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135DD884-5CC7-4FCF-B666-08AD3715EA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5865" yWindow="3075" windowWidth="18750" windowHeight="11610" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
   </bookViews>
   <sheets>
     <sheet name="품목마스터" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$326</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$330</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="336">
   <si>
     <t>제품코드</t>
   </si>
@@ -1041,6 +1041,18 @@
   </si>
   <si>
     <t>Big Bowl Shin Black 6</t>
+  </si>
+  <si>
+    <t>Big Bowl NFit Protein Spicy Beef VG 6</t>
+  </si>
+  <si>
+    <t>Big Bowl NFit Protein Spicy Beef 6</t>
+  </si>
+  <si>
+    <t>Big Bowl NFit Protein Mild Chicken 6</t>
+  </si>
+  <si>
+    <t>Shrimp Crackers 8 (RRP-pk) [K-US]</t>
   </si>
 </sst>
 </file>
@@ -3967,7 +3979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}">
-  <dimension ref="A1:D326"/>
+  <dimension ref="A1:D330"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
@@ -8236,10 +8248,10 @@
     </row>
     <row r="293" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
-        <v>101070220</v>
+        <v>101070215</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="C293" s="6" t="s">
         <v>35</v>
@@ -8250,12 +8262,12 @@
     </row>
     <row r="294" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
-        <v>101070221</v>
+        <v>101070216</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C294" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C294" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D294" t="s">
@@ -8264,12 +8276,12 @@
     </row>
     <row r="295" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
-        <v>101070222</v>
+        <v>101070217</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="C295" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C295" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D295" t="s">
@@ -8278,97 +8290,97 @@
     </row>
     <row r="296" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
+        <v>101070220</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D296" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="4">
+        <v>101070221</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D297" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A298" s="4">
+        <v>101070222</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D298" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="4">
         <v>101070224</v>
       </c>
-      <c r="B296" s="4" t="s">
+      <c r="B299" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C296" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D296" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A297" s="4">
+      <c r="C299" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D299" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="4">
         <v>101070232</v>
       </c>
-      <c r="B297" s="7" t="s">
+      <c r="B300" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C297" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D297" t="s">
+      <c r="C300" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D300" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A298" s="4">
+    <row r="301" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A301" s="4">
         <v>101070233</v>
       </c>
-      <c r="B298" s="7" t="s">
+      <c r="B301" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C298" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D298" t="s">
+      <c r="C301" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D301" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A299" s="4">
+    <row r="302" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="4">
         <v>101070237</v>
       </c>
-      <c r="B299" s="7" t="s">
+      <c r="B302" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="C299" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D299" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="4">
-        <v>102000296</v>
-      </c>
-      <c r="B300" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="C300" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D300" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="4">
-        <v>102000334</v>
-      </c>
-      <c r="B301" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="C301" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D301" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="4">
-        <v>102001999</v>
-      </c>
-      <c r="B302" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C302" s="5" t="s">
-        <v>71</v>
+      <c r="C302" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D302" t="s">
         <v>320</v>
@@ -8376,12 +8388,12 @@
     </row>
     <row r="303" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
-        <v>102002142</v>
+        <v>102000296</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C303" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C303" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D303" t="s">
@@ -8390,12 +8402,12 @@
     </row>
     <row r="304" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
-        <v>102002753</v>
+        <v>102000334</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C304" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C304" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D304" t="s">
@@ -8404,10 +8416,10 @@
     </row>
     <row r="305" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
-        <v>102002755</v>
+        <v>102001999</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="C305" s="5" t="s">
         <v>71</v>
@@ -8418,12 +8430,12 @@
     </row>
     <row r="306" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
-        <v>102002772</v>
+        <v>102002142</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C306" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C306" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D306" t="s">
@@ -8432,10 +8444,10 @@
     </row>
     <row r="307" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
-        <v>102002773</v>
+        <v>102002753</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C307" s="5" t="s">
         <v>71</v>
@@ -8446,12 +8458,12 @@
     </row>
     <row r="308" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
-        <v>102002774</v>
+        <v>102002755</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C308" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C308" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D308" t="s">
@@ -8460,12 +8472,12 @@
     </row>
     <row r="309" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
-        <v>102002775</v>
+        <v>102002772</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C309" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C309" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D309" t="s">
@@ -8474,10 +8486,10 @@
     </row>
     <row r="310" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>102070016</v>
+        <v>102002773</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="C310" s="5" t="s">
         <v>71</v>
@@ -8488,12 +8500,12 @@
     </row>
     <row r="311" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
-        <v>102070020</v>
+        <v>102002774</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="C311" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C311" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D311" t="s">
@@ -8502,12 +8514,12 @@
     </row>
     <row r="312" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
-        <v>102070038</v>
+        <v>102002775</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C312" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C312" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D312" t="s">
@@ -8516,10 +8528,10 @@
     </row>
     <row r="313" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
-        <v>102070041</v>
+        <v>102002780</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="C313" s="5" t="s">
         <v>71</v>
@@ -8530,12 +8542,12 @@
     </row>
     <row r="314" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
-        <v>102070042</v>
+        <v>102070016</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C314" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C314" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D314" t="s">
@@ -8544,10 +8556,10 @@
     </row>
     <row r="315" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A315" s="4">
-        <v>102070043</v>
+        <v>102070020</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>71</v>
@@ -8558,12 +8570,12 @@
     </row>
     <row r="316" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
-        <v>901001521</v>
+        <v>102070038</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C316" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C316" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D316" t="s">
@@ -8572,10 +8584,10 @@
     </row>
     <row r="317" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
-        <v>901001941</v>
+        <v>102070041</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C317" s="5" t="s">
         <v>71</v>
@@ -8586,12 +8598,12 @@
     </row>
     <row r="318" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
-        <v>901001955</v>
+        <v>102070042</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C318" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C318" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D318" t="s">
@@ -8600,10 +8612,10 @@
     </row>
     <row r="319" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
-        <v>901001956</v>
+        <v>102070043</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C319" s="5" t="s">
         <v>71</v>
@@ -8614,10 +8626,10 @@
     </row>
     <row r="320" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
-        <v>901001957</v>
+        <v>901001521</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C320" s="5" t="s">
         <v>71</v>
@@ -8628,10 +8640,10 @@
     </row>
     <row r="321" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>901001961</v>
+        <v>901001941</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C321" s="5" t="s">
         <v>71</v>
@@ -8642,10 +8654,10 @@
     </row>
     <row r="322" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
-        <v>901001964</v>
+        <v>901001955</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C322" s="5" t="s">
         <v>71</v>
@@ -8656,10 +8668,10 @@
     </row>
     <row r="323" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
-        <v>902000771</v>
+        <v>901001956</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>71</v>
@@ -8670,10 +8682,10 @@
     </row>
     <row r="324" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
-        <v>902070007</v>
+        <v>901001957</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C324" s="5" t="s">
         <v>71</v>
@@ -8684,10 +8696,10 @@
     </row>
     <row r="325" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
-        <v>903000582</v>
+        <v>901001961</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C325" s="5" t="s">
         <v>71</v>
@@ -8696,12 +8708,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
-        <v>903070001</v>
+        <v>901001964</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C326" s="5" t="s">
         <v>71</v>
@@ -8710,8 +8722,64 @@
         <v>320</v>
       </c>
     </row>
+    <row r="327" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="4">
+        <v>902000771</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D327" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="4">
+        <v>902070007</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D328" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A329" s="4">
+        <v>903000582</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D329" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A330" s="4">
+        <v>903070001</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D330" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D326" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
+  <autoFilter ref="A1:D330" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/_Master_Data/item_master.xlsx
+++ b/_Master_Data/item_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NSU_2027\Desktop\미국 공급망 고도화\1. 미국 주재원\비전2030(2026)\4.3.2 수요계획 강화\S&amp;OP\DashBoard 개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135DD884-5CC7-4FCF-B666-08AD3715EA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C189B55F-B104-4BC9-9769-DA47809F8A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
+    <workbookView xWindow="3090" yWindow="1950" windowWidth="23610" windowHeight="11850" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
   </bookViews>
   <sheets>
     <sheet name="품목마스터" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$330</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$332</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="338">
   <si>
     <t>제품코드</t>
   </si>
@@ -1053,6 +1053,12 @@
   </si>
   <si>
     <t>Shrimp Crackers 8 (RRP-pk) [K-US]</t>
+  </si>
+  <si>
+    <t>Bag(72) - Shin Black/Toomba [KDH]</t>
+  </si>
+  <si>
+    <t>Shrimp Crackers Spicy 8 (RRP-pk) [K-US]</t>
   </si>
 </sst>
 </file>
@@ -3979,7 +3985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}">
-  <dimension ref="A1:D330"/>
+  <dimension ref="A1:D332"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
@@ -8374,27 +8380,27 @@
     </row>
     <row r="302" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
+        <v>101070234</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D302" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A303" s="4">
         <v>101070237</v>
       </c>
-      <c r="B302" s="7" t="s">
+      <c r="B303" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="C302" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D302" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="4">
-        <v>102000296</v>
-      </c>
-      <c r="B303" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="C303" s="6" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D303" t="s">
         <v>320</v>
@@ -8402,10 +8408,10 @@
     </row>
     <row r="304" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
-        <v>102000334</v>
+        <v>102000296</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C304" s="6" t="s">
         <v>71</v>
@@ -8416,12 +8422,12 @@
     </row>
     <row r="305" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
-        <v>102001999</v>
+        <v>102000334</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C305" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C305" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D305" t="s">
@@ -8430,10 +8436,10 @@
     </row>
     <row r="306" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
-        <v>102002142</v>
+        <v>102001999</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C306" s="5" t="s">
         <v>71</v>
@@ -8444,10 +8450,10 @@
     </row>
     <row r="307" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
-        <v>102002753</v>
+        <v>102002142</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C307" s="5" t="s">
         <v>71</v>
@@ -8458,10 +8464,10 @@
     </row>
     <row r="308" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
-        <v>102002755</v>
+        <v>102002753</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="C308" s="5" t="s">
         <v>71</v>
@@ -8472,12 +8478,12 @@
     </row>
     <row r="309" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
-        <v>102002772</v>
+        <v>102002755</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C309" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C309" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D309" t="s">
@@ -8486,12 +8492,12 @@
     </row>
     <row r="310" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>102002773</v>
+        <v>102002772</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C310" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C310" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D310" t="s">
@@ -8500,12 +8506,12 @@
     </row>
     <row r="311" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
-        <v>102002774</v>
+        <v>102002773</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C311" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C311" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D311" t="s">
@@ -8514,12 +8520,12 @@
     </row>
     <row r="312" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
-        <v>102002775</v>
+        <v>102002774</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C312" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C312" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D312" t="s">
@@ -8528,10 +8534,10 @@
     </row>
     <row r="313" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
-        <v>102002780</v>
+        <v>102002775</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="C313" s="5" t="s">
         <v>71</v>
@@ -8542,10 +8548,10 @@
     </row>
     <row r="314" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
-        <v>102070016</v>
+        <v>102002780</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C314" s="5" t="s">
         <v>71</v>
@@ -8556,10 +8562,10 @@
     </row>
     <row r="315" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A315" s="4">
-        <v>102070020</v>
+        <v>102002784</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>71</v>
@@ -8570,12 +8576,12 @@
     </row>
     <row r="316" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
-        <v>102070038</v>
+        <v>102070016</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C316" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C316" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D316" t="s">
@@ -8584,10 +8590,10 @@
     </row>
     <row r="317" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
-        <v>102070041</v>
+        <v>102070020</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
         <v>71</v>
@@ -8598,10 +8604,10 @@
     </row>
     <row r="318" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
-        <v>102070042</v>
+        <v>102070038</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C318" s="6" t="s">
         <v>71</v>
@@ -8612,10 +8618,10 @@
     </row>
     <row r="319" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
-        <v>102070043</v>
+        <v>102070041</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C319" s="5" t="s">
         <v>71</v>
@@ -8626,12 +8632,12 @@
     </row>
     <row r="320" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
-        <v>901001521</v>
+        <v>102070042</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C320" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C320" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D320" t="s">
@@ -8640,10 +8646,10 @@
     </row>
     <row r="321" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>901001941</v>
+        <v>102070043</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C321" s="5" t="s">
         <v>71</v>
@@ -8654,10 +8660,10 @@
     </row>
     <row r="322" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
-        <v>901001955</v>
+        <v>901001521</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C322" s="5" t="s">
         <v>71</v>
@@ -8668,10 +8674,10 @@
     </row>
     <row r="323" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
-        <v>901001956</v>
+        <v>901001941</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>71</v>
@@ -8682,10 +8688,10 @@
     </row>
     <row r="324" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
-        <v>901001957</v>
+        <v>901001955</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C324" s="5" t="s">
         <v>71</v>
@@ -8696,10 +8702,10 @@
     </row>
     <row r="325" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
-        <v>901001961</v>
+        <v>901001956</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C325" s="5" t="s">
         <v>71</v>
@@ -8710,10 +8716,10 @@
     </row>
     <row r="326" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
-        <v>901001964</v>
+        <v>901001957</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C326" s="5" t="s">
         <v>71</v>
@@ -8724,10 +8730,10 @@
     </row>
     <row r="327" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
-        <v>902000771</v>
+        <v>901001961</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C327" s="5" t="s">
         <v>71</v>
@@ -8738,10 +8744,10 @@
     </row>
     <row r="328" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
-        <v>902070007</v>
+        <v>901001964</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C328" s="5" t="s">
         <v>71</v>
@@ -8752,10 +8758,10 @@
     </row>
     <row r="329" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
-        <v>903000582</v>
+        <v>902000771</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C329" s="5" t="s">
         <v>71</v>
@@ -8764,12 +8770,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
-        <v>903070001</v>
+        <v>902070007</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C330" s="5" t="s">
         <v>71</v>
@@ -8778,8 +8784,36 @@
         <v>320</v>
       </c>
     </row>
+    <row r="331" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A331" s="4">
+        <v>903000582</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D331" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A332" s="4">
+        <v>903070001</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D332" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D330" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
+  <autoFilter ref="A1:D332" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/_Master_Data/item_master.xlsx
+++ b/_Master_Data/item_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NSU_2027\Desktop\미국 공급망 고도화\1. 미국 주재원\비전2030(2026)\4.3.2 수요계획 강화\S&amp;OP\DashBoard 개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C189B55F-B104-4BC9-9769-DA47809F8A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F967411-D0F2-41E4-B7AF-2F44404BD50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="1950" windowWidth="23610" windowHeight="11850" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
   </bookViews>
   <sheets>
     <sheet name="품목마스터" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$332</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$338</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="344">
   <si>
     <t>제품코드</t>
   </si>
@@ -1059,6 +1059,24 @@
   </si>
   <si>
     <t>Shrimp Crackers Spicy 8 (RRP-pk) [K-US]</t>
+  </si>
+  <si>
+    <t>(E)Shin Signature 4Mix 16(SOxSBxSTxSGO)</t>
+  </si>
+  <si>
+    <t>(E)RChef 4Mix 16(RBGxRGCxRBBxRCC)</t>
+  </si>
+  <si>
+    <t>(E)Shin Original Kimchi 2Mix 8(SOxSKSF)</t>
+  </si>
+  <si>
+    <t>(E)Bowl Hot SVbeef 2Mix 6</t>
+  </si>
+  <si>
+    <t>(E)Bowl SVBeef SVChicken 2Mix 6</t>
+  </si>
+  <si>
+    <t>Shin Ramyun Gold Spicy Chicken 16 (4x4)</t>
   </si>
 </sst>
 </file>
@@ -3985,7 +4003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}">
-  <dimension ref="A1:D332"/>
+  <dimension ref="A1:D338"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
@@ -6552,14 +6570,13 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A174" s="2">
-        <v>102000276</v>
+        <v>101070244</v>
       </c>
       <c r="B174" t="s">
-        <v>177</v>
-      </c>
-      <c r="C174" t="str">
-        <f>VLOOKUP(A174,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
-        <v>TRA.GOODS</v>
+        <v>343</v>
+      </c>
+      <c r="C174" t="s">
+        <v>35</v>
       </c>
       <c r="D174" t="s">
         <v>320</v>
@@ -6567,10 +6584,10 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A175" s="2">
-        <v>102000283</v>
+        <v>102000276</v>
       </c>
       <c r="B175" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C175" t="str">
         <f>VLOOKUP(A175,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6582,10 +6599,10 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A176" s="2">
-        <v>102000288</v>
+        <v>102000283</v>
       </c>
       <c r="B176" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C176" t="str">
         <f>VLOOKUP(A176,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6597,10 +6614,10 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A177" s="2">
-        <v>102000305</v>
+        <v>102000288</v>
       </c>
       <c r="B177" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C177" t="str">
         <f>VLOOKUP(A177,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6612,10 +6629,10 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A178" s="2">
-        <v>102000382</v>
+        <v>102000305</v>
       </c>
       <c r="B178" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C178" t="str">
         <f>VLOOKUP(A178,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6627,10 +6644,10 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A179" s="2">
-        <v>102001162</v>
+        <v>102000382</v>
       </c>
       <c r="B179" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C179" t="str">
         <f>VLOOKUP(A179,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6642,10 +6659,10 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A180" s="2">
-        <v>102001521</v>
+        <v>102001162</v>
       </c>
       <c r="B180" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C180" t="str">
         <f>VLOOKUP(A180,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6657,10 +6674,10 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A181" s="2">
-        <v>102001641</v>
+        <v>102001521</v>
       </c>
       <c r="B181" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C181" t="str">
         <f>VLOOKUP(A181,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6672,10 +6689,10 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A182" s="2">
-        <v>102001743</v>
+        <v>102001641</v>
       </c>
       <c r="B182" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C182" t="str">
         <f>VLOOKUP(A182,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6687,10 +6704,10 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A183" s="2">
-        <v>102001744</v>
+        <v>102001743</v>
       </c>
       <c r="B183" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C183" t="str">
         <f>VLOOKUP(A183,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6702,10 +6719,10 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A184" s="2">
-        <v>102002006</v>
+        <v>102001744</v>
       </c>
       <c r="B184" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C184" t="str">
         <f>VLOOKUP(A184,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6717,10 +6734,10 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A185" s="2">
-        <v>102002009</v>
+        <v>102002006</v>
       </c>
       <c r="B185" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C185" t="str">
         <f>VLOOKUP(A185,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6732,10 +6749,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A186" s="2">
-        <v>102002018</v>
+        <v>102002009</v>
       </c>
       <c r="B186" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C186" t="str">
         <f>VLOOKUP(A186,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6747,10 +6764,10 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A187" s="2">
-        <v>102002020</v>
+        <v>102002018</v>
       </c>
       <c r="B187" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C187" t="str">
         <f>VLOOKUP(A187,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6762,10 +6779,10 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A188" s="2">
-        <v>102002033</v>
+        <v>102002020</v>
       </c>
       <c r="B188" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C188" t="str">
         <f>VLOOKUP(A188,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6777,10 +6794,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A189" s="2">
-        <v>102002036</v>
+        <v>102002033</v>
       </c>
       <c r="B189" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C189" t="str">
         <f>VLOOKUP(A189,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6792,10 +6809,10 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A190" s="2">
-        <v>102002037</v>
+        <v>102002036</v>
       </c>
       <c r="B190" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C190" t="str">
         <f>VLOOKUP(A190,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6807,10 +6824,10 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A191" s="2">
-        <v>102002069</v>
+        <v>102002037</v>
       </c>
       <c r="B191" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C191" t="str">
         <f>VLOOKUP(A191,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6822,10 +6839,10 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A192" s="2">
-        <v>102002140</v>
+        <v>102002069</v>
       </c>
       <c r="B192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C192" t="str">
         <f>VLOOKUP(A192,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6837,10 +6854,10 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A193" s="2">
-        <v>102002181</v>
+        <v>102002140</v>
       </c>
       <c r="B193" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C193" t="str">
         <f>VLOOKUP(A193,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6852,13 +6869,14 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A194" s="2">
-        <v>102002412</v>
+        <v>102002181</v>
       </c>
       <c r="B194" t="s">
-        <v>197</v>
-      </c>
-      <c r="C194" t="s">
-        <v>71</v>
+        <v>196</v>
+      </c>
+      <c r="C194" t="str">
+        <f>VLOOKUP(A194,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
+        <v>TRA.GOODS</v>
       </c>
       <c r="D194" t="s">
         <v>320</v>
@@ -6866,14 +6884,13 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A195" s="2">
-        <v>102002433</v>
+        <v>102002412</v>
       </c>
       <c r="B195" t="s">
-        <v>198</v>
-      </c>
-      <c r="C195" t="str">
-        <f>VLOOKUP(A195,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
-        <v>TRA.GOODS</v>
+        <v>197</v>
+      </c>
+      <c r="C195" t="s">
+        <v>71</v>
       </c>
       <c r="D195" t="s">
         <v>320</v>
@@ -6881,10 +6898,10 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A196" s="2">
-        <v>102002451</v>
+        <v>102002433</v>
       </c>
       <c r="B196" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C196" t="str">
         <f>VLOOKUP(A196,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6896,10 +6913,10 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A197" s="2">
-        <v>102002453</v>
+        <v>102002451</v>
       </c>
       <c r="B197" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C197" t="str">
         <f>VLOOKUP(A197,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6911,13 +6928,14 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A198" s="2">
-        <v>102002534</v>
+        <v>102002453</v>
       </c>
       <c r="B198" t="s">
-        <v>201</v>
-      </c>
-      <c r="C198" t="s">
-        <v>71</v>
+        <v>200</v>
+      </c>
+      <c r="C198" t="str">
+        <f>VLOOKUP(A198,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
+        <v>TRA.GOODS</v>
       </c>
       <c r="D198" t="s">
         <v>320</v>
@@ -6925,14 +6943,13 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A199" s="2">
-        <v>102002539</v>
+        <v>102002534</v>
       </c>
       <c r="B199" t="s">
-        <v>202</v>
-      </c>
-      <c r="C199" t="str">
-        <f>VLOOKUP(A199,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
-        <v>TRA.GOODS</v>
+        <v>201</v>
+      </c>
+      <c r="C199" t="s">
+        <v>71</v>
       </c>
       <c r="D199" t="s">
         <v>320</v>
@@ -6940,10 +6957,10 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A200" s="2">
-        <v>102002548</v>
+        <v>102002539</v>
       </c>
       <c r="B200" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C200" t="str">
         <f>VLOOKUP(A200,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6954,11 +6971,11 @@
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A201" s="3">
-        <v>102002568</v>
+      <c r="A201" s="2">
+        <v>102002548</v>
       </c>
       <c r="B201" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C201" t="str">
         <f>VLOOKUP(A201,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6969,11 +6986,11 @@
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A202" s="2">
-        <v>102002569</v>
+      <c r="A202" s="3">
+        <v>102002568</v>
       </c>
       <c r="B202" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C202" t="str">
         <f>VLOOKUP(A202,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -6985,10 +7002,10 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A203" s="2">
-        <v>102002584</v>
+        <v>102002569</v>
       </c>
       <c r="B203" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C203" t="str">
         <f>VLOOKUP(A203,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -7000,10 +7017,10 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A204" s="2">
-        <v>102002592</v>
+        <v>102002584</v>
       </c>
       <c r="B204" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C204" t="str">
         <f>VLOOKUP(A204,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -7015,10 +7032,10 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A205" s="2">
-        <v>102002642</v>
+        <v>102002592</v>
       </c>
       <c r="B205" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C205" t="str">
         <f>VLOOKUP(A205,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -7030,10 +7047,10 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A206" s="2">
-        <v>102002643</v>
+        <v>102002642</v>
       </c>
       <c r="B206" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C206" t="str">
         <f>VLOOKUP(A206,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -7045,10 +7062,10 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A207" s="2">
-        <v>102002666</v>
+        <v>102002643</v>
       </c>
       <c r="B207" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C207" t="str">
         <f>VLOOKUP(A207,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -7060,10 +7077,10 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A208" s="2">
-        <v>102002730</v>
+        <v>102002666</v>
       </c>
       <c r="B208" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C208" t="str">
         <f>VLOOKUP(A208,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -7075,10 +7092,10 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A209" s="2">
-        <v>102002731</v>
+        <v>102002730</v>
       </c>
       <c r="B209" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C209" t="str">
         <f>VLOOKUP(A209,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
@@ -7090,13 +7107,14 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A210" s="2">
-        <v>901002858</v>
+        <v>102002731</v>
       </c>
       <c r="B210" t="s">
-        <v>212</v>
-      </c>
-      <c r="C210" t="s">
-        <v>71</v>
+        <v>211</v>
+      </c>
+      <c r="C210" t="str">
+        <f>VLOOKUP(A210,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
+        <v>TRA.GOODS</v>
       </c>
       <c r="D210" t="s">
         <v>320</v>
@@ -7104,14 +7122,13 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A211" s="2">
-        <v>901002859</v>
+        <v>901002858</v>
       </c>
       <c r="B211" t="s">
-        <v>213</v>
-      </c>
-      <c r="C211" t="str">
-        <f>VLOOKUP(A211,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
-        <v>TRA.GOODS</v>
+        <v>212</v>
+      </c>
+      <c r="C211" t="s">
+        <v>71</v>
       </c>
       <c r="D211" t="s">
         <v>320</v>
@@ -7119,13 +7136,14 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A212" s="2">
-        <v>902000847</v>
+        <v>901002859</v>
       </c>
       <c r="B212" t="s">
-        <v>214</v>
-      </c>
-      <c r="C212" t="s">
-        <v>71</v>
+        <v>213</v>
+      </c>
+      <c r="C212" t="str">
+        <f>VLOOKUP(A212,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
+        <v>TRA.GOODS</v>
       </c>
       <c r="D212" t="s">
         <v>320</v>
@@ -7133,10 +7151,10 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A213" s="2">
-        <v>902000848</v>
+        <v>902000847</v>
       </c>
       <c r="B213" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C213" t="s">
         <v>71</v>
@@ -7145,30 +7163,30 @@
         <v>320</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A214" s="2">
+        <v>902000848</v>
+      </c>
+      <c r="B214" t="s">
+        <v>215</v>
+      </c>
+      <c r="C214" t="s">
+        <v>71</v>
+      </c>
+      <c r="D214" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="2">
         <v>902000868</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B215" t="s">
         <v>216</v>
       </c>
-      <c r="C214" t="str">
-        <f>VLOOKUP(A214,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
+      <c r="C215" t="str">
+        <f>VLOOKUP(A215,'[1]실적기반 수입분류'!$A$2:$C$224,3,FALSE)</f>
         <v>TRA.GOODS</v>
-      </c>
-      <c r="D214" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="4">
-        <v>101001850</v>
-      </c>
-      <c r="B215" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="D215" t="s">
         <v>320</v>
@@ -7176,26 +7194,26 @@
     </row>
     <row r="216" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
-        <v>101002158</v>
+        <v>101001850</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C216" s="6" t="s">
-        <v>35</v>
+        <v>217</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D216" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
-        <v>101002159</v>
+        <v>101002158</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C217" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C217" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D217" t="s">
@@ -7204,12 +7222,12 @@
     </row>
     <row r="218" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
-        <v>101002160</v>
+        <v>101002159</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C218" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C218" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D218" t="s">
@@ -7218,12 +7236,12 @@
     </row>
     <row r="219" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
-        <v>101002161</v>
+        <v>101002160</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C219" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C219" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D219" t="s">
@@ -7232,12 +7250,12 @@
     </row>
     <row r="220" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
-        <v>101002162</v>
+        <v>101002161</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C220" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C220" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D220" t="s">
@@ -7246,10 +7264,10 @@
     </row>
     <row r="221" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
-        <v>101002187</v>
+        <v>101002162</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>35</v>
@@ -7260,38 +7278,38 @@
     </row>
     <row r="222" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>101002227</v>
+        <v>101002187</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D222" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
-        <v>101002228</v>
+        <v>101002227</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C223" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C223" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D223" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
-        <v>101002244</v>
+        <v>101002228</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>35</v>
@@ -7302,12 +7320,12 @@
     </row>
     <row r="225" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
-        <v>101002613</v>
+        <v>101002244</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C225" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C225" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D225" t="s">
@@ -7316,26 +7334,26 @@
     </row>
     <row r="226" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
-        <v>101002646</v>
+        <v>101002613</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C226" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C226" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D226" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
-        <v>101002650</v>
+        <v>101002646</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C227" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C227" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D227" t="s">
@@ -7344,12 +7362,12 @@
     </row>
     <row r="228" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
-        <v>101002654</v>
+        <v>101002650</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="C228" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C228" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D228" t="s">
@@ -7358,12 +7376,12 @@
     </row>
     <row r="229" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
-        <v>101002655</v>
+        <v>101002654</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C229" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C229" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D229" t="s">
@@ -7372,26 +7390,26 @@
     </row>
     <row r="230" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
-        <v>101003028</v>
+        <v>101002655</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C230" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C230" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D230" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
-        <v>101003118</v>
+        <v>101003028</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C231" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C231" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D231" t="s">
@@ -7400,12 +7418,12 @@
     </row>
     <row r="232" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
-        <v>101003119</v>
+        <v>101003118</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C232" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C232" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D232" t="s">
@@ -7414,12 +7432,12 @@
     </row>
     <row r="233" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>101003122</v>
+        <v>101003119</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C233" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C233" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D233" t="s">
@@ -7428,12 +7446,12 @@
     </row>
     <row r="234" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
-        <v>101003207</v>
+        <v>101003122</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C234" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C234" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D234" t="s">
@@ -7442,12 +7460,12 @@
     </row>
     <row r="235" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
-        <v>101003236</v>
+        <v>101003207</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C235" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C235" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D235" t="s">
@@ -7456,10 +7474,10 @@
     </row>
     <row r="236" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
-        <v>101003242</v>
+        <v>101003236</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>35</v>
@@ -7470,24 +7488,24 @@
     </row>
     <row r="237" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
-        <v>101003264</v>
+        <v>101003242</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C237" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C237" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D237" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
-        <v>101003345</v>
+        <v>101003264</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>61</v>
+        <v>239</v>
       </c>
       <c r="C238" s="5" t="s">
         <v>35</v>
@@ -7498,12 +7516,12 @@
     </row>
     <row r="239" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
-        <v>101003370</v>
+        <v>101003345</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C239" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C239" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D239" t="s">
@@ -7512,12 +7530,12 @@
     </row>
     <row r="240" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
-        <v>101003418</v>
+        <v>101003370</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C240" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C240" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D240" t="s">
@@ -7526,66 +7544,66 @@
     </row>
     <row r="241" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
-        <v>101003449</v>
+        <v>101003418</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C241" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C241" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D241" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
-        <v>101003674</v>
+        <v>101003449</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C242" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C242" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D242" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
-        <v>101003941</v>
+        <v>101003674</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C243" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D243" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>101004114</v>
+        <v>101003941</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C244" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D244" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
-        <v>101004133</v>
+        <v>101004114</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C245" s="5" t="s">
         <v>35</v>
@@ -7596,26 +7614,26 @@
     </row>
     <row r="246" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
-        <v>101004148</v>
+        <v>101004133</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C246" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D246" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
-        <v>101004157</v>
+        <v>101004148</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="C247" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C247" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D247" t="s">
@@ -7624,26 +7642,26 @@
     </row>
     <row r="248" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
-        <v>101004167</v>
+        <v>101004157</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="C248" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C248" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D248" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
-        <v>101004173</v>
+        <v>101004167</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C249" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C249" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D249" t="s">
@@ -7652,10 +7670,10 @@
     </row>
     <row r="250" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
-        <v>101004175</v>
+        <v>101004173</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C250" s="6" t="s">
         <v>35</v>
@@ -7666,24 +7684,24 @@
     </row>
     <row r="251" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
-        <v>101004182</v>
+        <v>101004175</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C251" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C251" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D251" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
-        <v>101004189</v>
+        <v>101004182</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C252" s="5" t="s">
         <v>35</v>
@@ -7694,12 +7712,12 @@
     </row>
     <row r="253" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
-        <v>101004190</v>
+        <v>101004189</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C253" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C253" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D253" t="s">
@@ -7708,40 +7726,40 @@
     </row>
     <row r="254" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
-        <v>101004200</v>
+        <v>101004190</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C254" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D254" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>101004220</v>
+        <v>101004200</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C255" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C255" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D255" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
-        <v>101004226</v>
+        <v>101004220</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C256" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C256" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D256" t="s">
@@ -7750,12 +7768,12 @@
     </row>
     <row r="257" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
-        <v>101004227</v>
+        <v>101004226</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="C257" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C257" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D257" t="s">
@@ -7764,12 +7782,12 @@
     </row>
     <row r="258" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
-        <v>101004231</v>
+        <v>101004227</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C258" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C258" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D258" t="s">
@@ -7778,10 +7796,10 @@
     </row>
     <row r="259" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
-        <v>101004240</v>
+        <v>101004231</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C259" s="6" t="s">
         <v>35</v>
@@ -7792,10 +7810,10 @@
     </row>
     <row r="260" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
-        <v>101004246</v>
+        <v>101004240</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C260" s="6" t="s">
         <v>35</v>
@@ -7806,12 +7824,12 @@
     </row>
     <row r="261" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
-        <v>101004247</v>
+        <v>101004246</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C261" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C261" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D261" t="s">
@@ -7820,12 +7838,12 @@
     </row>
     <row r="262" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
-        <v>101004256</v>
+        <v>101004247</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C262" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C262" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D262" t="s">
@@ -7834,12 +7852,12 @@
     </row>
     <row r="263" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
-        <v>101004262</v>
+        <v>101004256</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="C263" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C263" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D263" t="s">
@@ -7848,24 +7866,24 @@
     </row>
     <row r="264" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
-        <v>101005414</v>
+        <v>101004262</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C264" s="6" t="s">
-        <v>71</v>
+        <v>264</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D264" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
-        <v>101005623</v>
+        <v>101005414</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C265" s="6" t="s">
         <v>71</v>
@@ -7876,13 +7894,13 @@
     </row>
     <row r="266" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>101005699</v>
+        <v>101005623</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D266" t="s">
         <v>320</v>
@@ -7890,12 +7908,12 @@
     </row>
     <row r="267" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
-        <v>101005738</v>
+        <v>101005699</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="C267" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C267" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D267" t="s">
@@ -7904,13 +7922,13 @@
     </row>
     <row r="268" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
-        <v>101070021</v>
+        <v>101005738</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="C268" s="6" t="s">
-        <v>71</v>
+        <v>268</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D268" t="s">
         <v>320</v>
@@ -7918,26 +7936,26 @@
     </row>
     <row r="269" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
-        <v>101070041</v>
+        <v>101070021</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D269" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
-        <v>101070042</v>
+        <v>101070041</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C270" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C270" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D270" t="s">
@@ -7946,12 +7964,12 @@
     </row>
     <row r="271" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
-        <v>101070043</v>
+        <v>101070042</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="C271" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C271" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D271" t="s">
@@ -7960,40 +7978,40 @@
     </row>
     <row r="272" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
-        <v>101070101</v>
+        <v>101070043</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C272" s="5" t="s">
-        <v>71</v>
+        <v>272</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D272" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
-        <v>101070113</v>
+        <v>101070101</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="C273" s="6" t="s">
-        <v>35</v>
+        <v>273</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D273" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
-        <v>101070114</v>
+        <v>101070113</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C274" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C274" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D274" t="s">
@@ -8002,40 +8020,40 @@
     </row>
     <row r="275" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
-        <v>101070119</v>
+        <v>101070114</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C275" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C275" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D275" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
-        <v>101070146</v>
+        <v>101070119</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C276" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D276" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>101070147</v>
+        <v>101070146</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="C277" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C277" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D277" t="s">
@@ -8044,10 +8062,10 @@
     </row>
     <row r="278" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
-        <v>101070173</v>
+        <v>101070147</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="C278" s="5" t="s">
         <v>35</v>
@@ -8058,12 +8076,12 @@
     </row>
     <row r="279" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
-        <v>101070175</v>
+        <v>101070173</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="C279" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C279" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D279" t="s">
@@ -8072,12 +8090,12 @@
     </row>
     <row r="280" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
-        <v>101070176</v>
+        <v>101070175</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C280" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C280" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D280" t="s">
@@ -8086,10 +8104,10 @@
     </row>
     <row r="281" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
-        <v>101070177</v>
+        <v>101070176</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>322</v>
+        <v>280</v>
       </c>
       <c r="C281" s="5" t="s">
         <v>35</v>
@@ -8100,10 +8118,10 @@
     </row>
     <row r="282" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
-        <v>101070178</v>
+        <v>101070177</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C282" s="5" t="s">
         <v>35</v>
@@ -8114,12 +8132,12 @@
     </row>
     <row r="283" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
-        <v>101070179</v>
+        <v>101070178</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C283" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C283" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D283" t="s">
@@ -8128,26 +8146,26 @@
     </row>
     <row r="284" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
-        <v>101070183</v>
+        <v>101070179</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C284" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C284" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D284" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
-        <v>101070184</v>
+        <v>101070183</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="C285" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C285" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D285" t="s">
@@ -8156,12 +8174,12 @@
     </row>
     <row r="286" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
-        <v>101070185</v>
+        <v>101070184</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="C286" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C286" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D286" t="s">
@@ -8170,12 +8188,12 @@
     </row>
     <row r="287" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
-        <v>101070186</v>
+        <v>101070185</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C287" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C287" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D287" t="s">
@@ -8184,10 +8202,10 @@
     </row>
     <row r="288" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>101070197</v>
+        <v>101070186</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>327</v>
+        <v>285</v>
       </c>
       <c r="C288" s="6" t="s">
         <v>35</v>
@@ -8198,10 +8216,10 @@
     </row>
     <row r="289" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
-        <v>101070203</v>
+        <v>101070195</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="C289" s="6" t="s">
         <v>35</v>
@@ -8212,13 +8230,13 @@
     </row>
     <row r="290" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
-        <v>101070204</v>
+        <v>101070197</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C290" s="5" t="s">
-        <v>71</v>
+        <v>327</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D290" t="s">
         <v>320</v>
@@ -8226,10 +8244,10 @@
     </row>
     <row r="291" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
-        <v>101070205</v>
+        <v>101070200</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="C291" s="6" t="s">
         <v>35</v>
@@ -8240,13 +8258,13 @@
     </row>
     <row r="292" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
-        <v>101070209</v>
+        <v>101070203</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="C292" s="5" t="s">
-        <v>71</v>
+        <v>286</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D292" t="s">
         <v>320</v>
@@ -8254,13 +8272,13 @@
     </row>
     <row r="293" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
-        <v>101070215</v>
+        <v>101070204</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="C293" s="6" t="s">
-        <v>35</v>
+        <v>287</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D293" t="s">
         <v>320</v>
@@ -8268,10 +8286,10 @@
     </row>
     <row r="294" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
-        <v>101070216</v>
+        <v>101070205</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>332</v>
+        <v>288</v>
       </c>
       <c r="C294" s="6" t="s">
         <v>35</v>
@@ -8282,10 +8300,10 @@
     </row>
     <row r="295" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
-        <v>101070217</v>
+        <v>101070208</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C295" s="6" t="s">
         <v>35</v>
@@ -8296,13 +8314,13 @@
     </row>
     <row r="296" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
-        <v>101070220</v>
+        <v>101070209</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C296" s="6" t="s">
-        <v>35</v>
+        <v>289</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D296" t="s">
         <v>320</v>
@@ -8310,12 +8328,12 @@
     </row>
     <row r="297" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
-        <v>101070221</v>
+        <v>101070215</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C297" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C297" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D297" t="s">
@@ -8324,12 +8342,12 @@
     </row>
     <row r="298" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
-        <v>101070222</v>
+        <v>101070216</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="C298" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C298" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D298" t="s">
@@ -8338,66 +8356,66 @@
     </row>
     <row r="299" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
+        <v>101070217</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D299" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="4">
+        <v>101070220</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D300" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="4">
+        <v>101070221</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D301" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="4">
+        <v>101070222</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D302" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A303" s="4">
         <v>101070224</v>
       </c>
-      <c r="B299" s="4" t="s">
+      <c r="B303" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="C299" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D299" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="4">
-        <v>101070232</v>
-      </c>
-      <c r="B300" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C300" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D300" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A301" s="4">
-        <v>101070233</v>
-      </c>
-      <c r="B301" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="C301" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D301" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A302" s="4">
-        <v>101070234</v>
-      </c>
-      <c r="B302" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="C302" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D302" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A303" s="4">
-        <v>101070237</v>
-      </c>
-      <c r="B303" s="7" t="s">
-        <v>331</v>
       </c>
       <c r="C303" s="6" t="s">
         <v>35</v>
@@ -8408,13 +8426,13 @@
     </row>
     <row r="304" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
-        <v>102000296</v>
-      </c>
-      <c r="B304" s="4" t="s">
-        <v>293</v>
+        <v>101070226</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>341</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D304" t="s">
         <v>320</v>
@@ -8422,69 +8440,69 @@
     </row>
     <row r="305" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
-        <v>102000334</v>
-      </c>
-      <c r="B305" s="4" t="s">
-        <v>294</v>
+        <v>101070227</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D305" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
-        <v>102001999</v>
-      </c>
-      <c r="B306" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C306" s="5" t="s">
-        <v>71</v>
+        <v>101070232</v>
+      </c>
+      <c r="B306" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D306" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
-        <v>102002142</v>
-      </c>
-      <c r="B307" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C307" s="5" t="s">
-        <v>71</v>
+        <v>101070233</v>
+      </c>
+      <c r="B307" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D307" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
-        <v>102002753</v>
-      </c>
-      <c r="B308" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>71</v>
+        <v>101070234</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D308" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
-        <v>102002755</v>
-      </c>
-      <c r="B309" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="C309" s="5" t="s">
-        <v>71</v>
+        <v>101070237</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D309" t="s">
         <v>320</v>
@@ -8492,10 +8510,10 @@
     </row>
     <row r="310" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>102002772</v>
+        <v>102000296</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C310" s="6" t="s">
         <v>71</v>
@@ -8506,12 +8524,12 @@
     </row>
     <row r="311" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
-        <v>102002773</v>
+        <v>102000334</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C311" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C311" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D311" t="s">
@@ -8520,12 +8538,12 @@
     </row>
     <row r="312" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
-        <v>102002774</v>
+        <v>102001999</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C312" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C312" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D312" t="s">
@@ -8534,10 +8552,10 @@
     </row>
     <row r="313" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
-        <v>102002775</v>
+        <v>102002142</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C313" s="5" t="s">
         <v>71</v>
@@ -8548,10 +8566,10 @@
     </row>
     <row r="314" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
-        <v>102002780</v>
+        <v>102002753</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>335</v>
+        <v>297</v>
       </c>
       <c r="C314" s="5" t="s">
         <v>71</v>
@@ -8562,10 +8580,10 @@
     </row>
     <row r="315" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A315" s="4">
-        <v>102002784</v>
+        <v>102002755</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>71</v>
@@ -8576,12 +8594,12 @@
     </row>
     <row r="316" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
-        <v>102070016</v>
+        <v>102002772</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="C316" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C316" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D316" t="s">
@@ -8590,10 +8608,10 @@
     </row>
     <row r="317" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
-        <v>102070020</v>
+        <v>102002773</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="C317" s="5" t="s">
         <v>71</v>
@@ -8604,10 +8622,10 @@
     </row>
     <row r="318" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
-        <v>102070038</v>
+        <v>102002774</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C318" s="6" t="s">
         <v>71</v>
@@ -8618,10 +8636,10 @@
     </row>
     <row r="319" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
-        <v>102070041</v>
+        <v>102002775</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C319" s="5" t="s">
         <v>71</v>
@@ -8632,12 +8650,12 @@
     </row>
     <row r="320" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
-        <v>102070042</v>
+        <v>102002780</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C320" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="C320" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D320" t="s">
@@ -8646,10 +8664,10 @@
     </row>
     <row r="321" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>102070043</v>
+        <v>102002784</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="C321" s="5" t="s">
         <v>71</v>
@@ -8660,10 +8678,10 @@
     </row>
     <row r="322" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
-        <v>901001521</v>
+        <v>102070016</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C322" s="5" t="s">
         <v>71</v>
@@ -8674,10 +8692,10 @@
     </row>
     <row r="323" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
-        <v>901001941</v>
+        <v>102070020</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>71</v>
@@ -8688,12 +8706,12 @@
     </row>
     <row r="324" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
-        <v>901001955</v>
+        <v>102070038</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C324" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C324" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D324" t="s">
@@ -8702,10 +8720,10 @@
     </row>
     <row r="325" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
-        <v>901001956</v>
+        <v>102070041</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C325" s="5" t="s">
         <v>71</v>
@@ -8716,12 +8734,12 @@
     </row>
     <row r="326" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
-        <v>901001957</v>
+        <v>102070042</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C326" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C326" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D326" t="s">
@@ -8730,10 +8748,10 @@
     </row>
     <row r="327" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
-        <v>901001961</v>
+        <v>102070043</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C327" s="5" t="s">
         <v>71</v>
@@ -8744,10 +8762,10 @@
     </row>
     <row r="328" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
-        <v>901001964</v>
+        <v>901001521</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C328" s="5" t="s">
         <v>71</v>
@@ -8758,10 +8776,10 @@
     </row>
     <row r="329" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
-        <v>902000771</v>
+        <v>901001941</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C329" s="5" t="s">
         <v>71</v>
@@ -8772,10 +8790,10 @@
     </row>
     <row r="330" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
-        <v>902070007</v>
+        <v>901001955</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C330" s="5" t="s">
         <v>71</v>
@@ -8786,10 +8804,10 @@
     </row>
     <row r="331" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4">
-        <v>903000582</v>
+        <v>901001956</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C331" s="5" t="s">
         <v>71</v>
@@ -8798,12 +8816,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>903070001</v>
+        <v>901001957</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C332" s="5" t="s">
         <v>71</v>
@@ -8812,8 +8830,92 @@
         <v>320</v>
       </c>
     </row>
+    <row r="333" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A333" s="4">
+        <v>901001961</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D333" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A334" s="4">
+        <v>901001964</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C334" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D334" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A335" s="4">
+        <v>902000771</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C335" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D335" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A336" s="4">
+        <v>902070007</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C336" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D336" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A337" s="4">
+        <v>903000582</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C337" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D337" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A338" s="4">
+        <v>903070001</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D338" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D332" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
+  <autoFilter ref="A1:D338" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/_Master_Data/item_master.xlsx
+++ b/_Master_Data/item_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NSU_2027\Desktop\미국 공급망 고도화\1. 미국 주재원\비전2030(2026)\4.3.2 수요계획 강화\S&amp;OP\DashBoard 개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F967411-D0F2-41E4-B7AF-2F44404BD50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534B52FF-435D-46AB-B991-7A03A46D5159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
+    <workbookView xWindow="8415" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
   </bookViews>
   <sheets>
     <sheet name="품목마스터" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$338</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$339</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="345">
   <si>
     <t>제품코드</t>
   </si>
@@ -1077,6 +1077,9 @@
   </si>
   <si>
     <t>Shin Ramyun Gold Spicy Chicken 16 (4x4)</t>
+  </si>
+  <si>
+    <t>Shrimp Crackers Wasabi 8 (RRP-pk) [K-US]</t>
   </si>
 </sst>
 </file>
@@ -4003,7 +4006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}">
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D339"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
@@ -8678,10 +8681,10 @@
     </row>
     <row r="322" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
-        <v>102070016</v>
+        <v>102002785</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="C322" s="5" t="s">
         <v>71</v>
@@ -8692,10 +8695,10 @@
     </row>
     <row r="323" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
-        <v>102070020</v>
+        <v>102070016</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>71</v>
@@ -8706,12 +8709,12 @@
     </row>
     <row r="324" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
-        <v>102070038</v>
+        <v>102070020</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C324" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C324" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D324" t="s">
@@ -8720,12 +8723,12 @@
     </row>
     <row r="325" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
-        <v>102070041</v>
+        <v>102070038</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C325" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C325" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D325" t="s">
@@ -8734,12 +8737,12 @@
     </row>
     <row r="326" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
-        <v>102070042</v>
+        <v>102070041</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C326" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C326" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D326" t="s">
@@ -8748,12 +8751,12 @@
     </row>
     <row r="327" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
-        <v>102070043</v>
+        <v>102070042</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="C327" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C327" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D327" t="s">
@@ -8762,10 +8765,10 @@
     </row>
     <row r="328" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
-        <v>901001521</v>
+        <v>102070043</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C328" s="5" t="s">
         <v>71</v>
@@ -8776,10 +8779,10 @@
     </row>
     <row r="329" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
-        <v>901001941</v>
+        <v>901001521</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C329" s="5" t="s">
         <v>71</v>
@@ -8790,10 +8793,10 @@
     </row>
     <row r="330" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
-        <v>901001955</v>
+        <v>901001941</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C330" s="5" t="s">
         <v>71</v>
@@ -8804,10 +8807,10 @@
     </row>
     <row r="331" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4">
-        <v>901001956</v>
+        <v>901001955</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C331" s="5" t="s">
         <v>71</v>
@@ -8818,10 +8821,10 @@
     </row>
     <row r="332" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>901001957</v>
+        <v>901001956</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C332" s="5" t="s">
         <v>71</v>
@@ -8832,10 +8835,10 @@
     </row>
     <row r="333" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4">
-        <v>901001961</v>
+        <v>901001957</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C333" s="5" t="s">
         <v>71</v>
@@ -8846,10 +8849,10 @@
     </row>
     <row r="334" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4">
-        <v>901001964</v>
+        <v>901001961</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C334" s="5" t="s">
         <v>71</v>
@@ -8860,10 +8863,10 @@
     </row>
     <row r="335" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4">
-        <v>902000771</v>
+        <v>901001964</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C335" s="5" t="s">
         <v>71</v>
@@ -8874,10 +8877,10 @@
     </row>
     <row r="336" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4">
-        <v>902070007</v>
+        <v>902000771</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C336" s="5" t="s">
         <v>71</v>
@@ -8888,10 +8891,10 @@
     </row>
     <row r="337" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4">
-        <v>903000582</v>
+        <v>902070007</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C337" s="5" t="s">
         <v>71</v>
@@ -8900,12 +8903,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4">
-        <v>903070001</v>
+        <v>903000582</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C338" s="5" t="s">
         <v>71</v>
@@ -8914,8 +8917,22 @@
         <v>320</v>
       </c>
     </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A339" s="4">
+        <v>903070001</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C339" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D339" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D338" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
+  <autoFilter ref="A1:D339" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/_Master_Data/item_master.xlsx
+++ b/_Master_Data/item_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NSU_2027\Desktop\미국 공급망 고도화\1. 미국 주재원\비전2030(2026)\4.3.2 수요계획 강화\S&amp;OP\DashBoard 개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534B52FF-435D-46AB-B991-7A03A46D5159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C45D1D-2794-476B-8DB3-73E0818ED884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8415" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
+    <workbookView xWindow="9975" yWindow="3285" windowWidth="17280" windowHeight="10005" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
   </bookViews>
   <sheets>
     <sheet name="품목마스터" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$339</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$345</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="351">
   <si>
     <t>제품코드</t>
   </si>
@@ -1080,6 +1080,24 @@
   </si>
   <si>
     <t>Shrimp Crackers Wasabi 8 (RRP-pk) [K-US]</t>
+  </si>
+  <si>
+    <t>(E)Bowl Shin SVBeef 2Mix 6</t>
+  </si>
+  <si>
+    <t>(E)Bowl Shin Hot 2Mix 6</t>
+  </si>
+  <si>
+    <t>(E)Bowl Shin Kimchi 2Mix 6</t>
+  </si>
+  <si>
+    <t>(E)Bowl Hot Kimchi 2Mix 6</t>
+  </si>
+  <si>
+    <t>(E)Shin Rabokki 2Mix 8(TxSO)</t>
+  </si>
+  <si>
+    <t>(E)Shin Global 4Mix 16(SOxSBxSGOxSTOM)</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1179,6 +1197,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4006,7 +4027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}">
-  <dimension ref="A1:D339"/>
+  <dimension ref="A1:D345"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
@@ -8233,13 +8254,13 @@
     </row>
     <row r="290" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
-        <v>101070197</v>
+        <v>101070196</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C290" s="6" t="s">
-        <v>35</v>
+        <v>350</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D290" t="s">
         <v>320</v>
@@ -8247,10 +8268,10 @@
     </row>
     <row r="291" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
-        <v>101070200</v>
+        <v>101070197</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="C291" s="6" t="s">
         <v>35</v>
@@ -8261,10 +8282,10 @@
     </row>
     <row r="292" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
-        <v>101070203</v>
+        <v>101070200</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="C292" s="6" t="s">
         <v>35</v>
@@ -8275,13 +8296,13 @@
     </row>
     <row r="293" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
-        <v>101070204</v>
+        <v>101070203</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C293" s="5" t="s">
-        <v>71</v>
+        <v>286</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D293" t="s">
         <v>320</v>
@@ -8289,13 +8310,13 @@
     </row>
     <row r="294" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
-        <v>101070205</v>
+        <v>101070204</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="C294" s="6" t="s">
-        <v>35</v>
+        <v>287</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D294" t="s">
         <v>320</v>
@@ -8303,10 +8324,10 @@
     </row>
     <row r="295" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
-        <v>101070208</v>
+        <v>101070205</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>340</v>
+        <v>288</v>
       </c>
       <c r="C295" s="6" t="s">
         <v>35</v>
@@ -8317,13 +8338,13 @@
     </row>
     <row r="296" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
-        <v>101070209</v>
+        <v>101070208</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="C296" s="5" t="s">
-        <v>71</v>
+        <v>340</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D296" t="s">
         <v>320</v>
@@ -8331,13 +8352,13 @@
     </row>
     <row r="297" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
-        <v>101070215</v>
+        <v>101070209</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="C297" s="6" t="s">
-        <v>35</v>
+        <v>289</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D297" t="s">
         <v>320</v>
@@ -8345,10 +8366,10 @@
     </row>
     <row r="298" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
-        <v>101070216</v>
+        <v>101070215</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C298" s="6" t="s">
         <v>35</v>
@@ -8359,10 +8380,10 @@
     </row>
     <row r="299" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>101070217</v>
+        <v>101070216</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C299" s="6" t="s">
         <v>35</v>
@@ -8373,10 +8394,10 @@
     </row>
     <row r="300" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
-        <v>101070220</v>
+        <v>101070217</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="C300" s="6" t="s">
         <v>35</v>
@@ -8387,13 +8408,13 @@
     </row>
     <row r="301" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
-        <v>101070221</v>
+        <v>101070218</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D301" t="s">
         <v>320</v>
@@ -8401,12 +8422,12 @@
     </row>
     <row r="302" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
-        <v>101070222</v>
+        <v>101070220</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="C302" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C302" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D302" t="s">
@@ -8415,12 +8436,12 @@
     </row>
     <row r="303" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
-        <v>101070224</v>
+        <v>101070221</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C303" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C303" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D303" t="s">
@@ -8429,12 +8450,12 @@
     </row>
     <row r="304" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
-        <v>101070226</v>
-      </c>
-      <c r="B304" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="C304" s="6" t="s">
+        <v>101070222</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C304" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D304" t="s">
@@ -8443,53 +8464,53 @@
     </row>
     <row r="305" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
+        <v>101070224</v>
+      </c>
+      <c r="B305" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D305" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A306" s="4">
+        <v>101070225</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D306" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="4">
+        <v>101070226</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D307" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="4">
         <v>101070227</v>
       </c>
-      <c r="B305" s="5" t="s">
+      <c r="B308" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="C305" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D305" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A306" s="4">
-        <v>101070232</v>
-      </c>
-      <c r="B306" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C306" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D306" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="4">
-        <v>101070233</v>
-      </c>
-      <c r="B307" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="C307" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D307" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A308" s="4">
-        <v>101070234</v>
-      </c>
-      <c r="B308" s="7" t="s">
-        <v>336</v>
-      </c>
       <c r="C308" s="6" t="s">
         <v>35</v>
       </c>
@@ -8497,12 +8518,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
-        <v>101070237</v>
-      </c>
-      <c r="B309" s="7" t="s">
-        <v>331</v>
+        <v>101070228</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>346</v>
       </c>
       <c r="C309" s="6" t="s">
         <v>35</v>
@@ -8513,13 +8534,13 @@
     </row>
     <row r="310" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>102000296</v>
-      </c>
-      <c r="B310" s="4" t="s">
-        <v>293</v>
+        <v>101070229</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>347</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D310" t="s">
         <v>320</v>
@@ -8527,69 +8548,69 @@
     </row>
     <row r="311" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
-        <v>102000334</v>
-      </c>
-      <c r="B311" s="4" t="s">
-        <v>294</v>
+        <v>101070230</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>345</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D311" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
-        <v>102001999</v>
-      </c>
-      <c r="B312" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C312" s="5" t="s">
-        <v>71</v>
+        <v>101070232</v>
+      </c>
+      <c r="B312" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D312" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
-        <v>102002142</v>
-      </c>
-      <c r="B313" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C313" s="5" t="s">
-        <v>71</v>
+        <v>101070233</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D313" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
-        <v>102002753</v>
-      </c>
-      <c r="B314" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C314" s="5" t="s">
-        <v>71</v>
+        <v>101070234</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D314" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
-        <v>102002755</v>
-      </c>
-      <c r="B315" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="C315" s="5" t="s">
-        <v>71</v>
+        <v>101070237</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D315" t="s">
         <v>320</v>
@@ -8597,10 +8618,10 @@
     </row>
     <row r="316" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
-        <v>102002772</v>
+        <v>102000296</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C316" s="6" t="s">
         <v>71</v>
@@ -8611,12 +8632,12 @@
     </row>
     <row r="317" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
-        <v>102002773</v>
+        <v>102000334</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C317" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C317" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D317" t="s">
@@ -8625,12 +8646,12 @@
     </row>
     <row r="318" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
-        <v>102002774</v>
+        <v>102001999</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C318" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C318" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D318" t="s">
@@ -8639,10 +8660,10 @@
     </row>
     <row r="319" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
-        <v>102002775</v>
+        <v>102002142</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C319" s="5" t="s">
         <v>71</v>
@@ -8653,10 +8674,10 @@
     </row>
     <row r="320" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
-        <v>102002780</v>
+        <v>102002753</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>335</v>
+        <v>297</v>
       </c>
       <c r="C320" s="5" t="s">
         <v>71</v>
@@ -8667,10 +8688,10 @@
     </row>
     <row r="321" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>102002784</v>
+        <v>102002755</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="C321" s="5" t="s">
         <v>71</v>
@@ -8681,12 +8702,12 @@
     </row>
     <row r="322" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
-        <v>102002785</v>
+        <v>102002772</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="C322" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C322" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D322" t="s">
@@ -8695,10 +8716,10 @@
     </row>
     <row r="323" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
-        <v>102070016</v>
+        <v>102002773</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>71</v>
@@ -8709,12 +8730,12 @@
     </row>
     <row r="324" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
-        <v>102070020</v>
+        <v>102002774</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="C324" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C324" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D324" t="s">
@@ -8723,12 +8744,12 @@
     </row>
     <row r="325" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
-        <v>102070038</v>
+        <v>102002775</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C325" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C325" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D325" t="s">
@@ -8737,10 +8758,10 @@
     </row>
     <row r="326" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
-        <v>102070041</v>
+        <v>102002780</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="C326" s="5" t="s">
         <v>71</v>
@@ -8751,12 +8772,12 @@
     </row>
     <row r="327" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
-        <v>102070042</v>
+        <v>102002784</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C327" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C327" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D327" t="s">
@@ -8765,10 +8786,10 @@
     </row>
     <row r="328" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
-        <v>102070043</v>
+        <v>102002785</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="C328" s="5" t="s">
         <v>71</v>
@@ -8779,10 +8800,10 @@
     </row>
     <row r="329" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
-        <v>901001521</v>
+        <v>102070016</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C329" s="5" t="s">
         <v>71</v>
@@ -8793,10 +8814,10 @@
     </row>
     <row r="330" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
-        <v>901001941</v>
+        <v>102070020</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C330" s="5" t="s">
         <v>71</v>
@@ -8807,12 +8828,12 @@
     </row>
     <row r="331" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4">
-        <v>901001955</v>
+        <v>102070038</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C331" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C331" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D331" t="s">
@@ -8821,10 +8842,10 @@
     </row>
     <row r="332" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>901001956</v>
+        <v>102070041</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C332" s="5" t="s">
         <v>71</v>
@@ -8835,12 +8856,12 @@
     </row>
     <row r="333" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4">
-        <v>901001957</v>
+        <v>102070042</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C333" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C333" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D333" t="s">
@@ -8849,10 +8870,10 @@
     </row>
     <row r="334" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4">
-        <v>901001961</v>
+        <v>102070043</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C334" s="5" t="s">
         <v>71</v>
@@ -8863,10 +8884,10 @@
     </row>
     <row r="335" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4">
-        <v>901001964</v>
+        <v>901001521</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C335" s="5" t="s">
         <v>71</v>
@@ -8877,10 +8898,10 @@
     </row>
     <row r="336" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4">
-        <v>902000771</v>
+        <v>901001941</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C336" s="5" t="s">
         <v>71</v>
@@ -8891,10 +8912,10 @@
     </row>
     <row r="337" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4">
-        <v>902070007</v>
+        <v>901001955</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C337" s="5" t="s">
         <v>71</v>
@@ -8905,10 +8926,10 @@
     </row>
     <row r="338" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4">
-        <v>903000582</v>
+        <v>901001956</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C338" s="5" t="s">
         <v>71</v>
@@ -8917,12 +8938,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A339" s="4">
-        <v>903070001</v>
+        <v>901001957</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C339" s="5" t="s">
         <v>71</v>
@@ -8931,8 +8952,92 @@
         <v>320</v>
       </c>
     </row>
+    <row r="340" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A340" s="4">
+        <v>901001961</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D340" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="4">
+        <v>901001964</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D341" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A342" s="4">
+        <v>902000771</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D342" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A343" s="4">
+        <v>902070007</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D343" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A344" s="4">
+        <v>903000582</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D344" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A345" s="4">
+        <v>903070001</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C345" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D345" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D339" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
+  <autoFilter ref="A1:D345" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/_Master_Data/item_master.xlsx
+++ b/_Master_Data/item_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NSU_2027\Desktop\미국 공급망 고도화\1. 미국 주재원\비전2030(2026)\4.3.2 수요계획 강화\S&amp;OP\DashBoard 개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C45D1D-2794-476B-8DB3-73E0818ED884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5964A0AE-8C43-4B2E-ACAC-E224CA4C4062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9975" yWindow="3285" windowWidth="17280" windowHeight="10005" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
   </bookViews>
   <sheets>
     <sheet name="품목마스터" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$345</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$347</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="353">
   <si>
     <t>제품코드</t>
   </si>
@@ -1098,6 +1098,12 @@
   </si>
   <si>
     <t>(E)Shin Global 4Mix 16(SOxSBxSGOxSTOM)</t>
+  </si>
+  <si>
+    <t>Cuttlefish Snack 8 (M-pk) [K-US]</t>
+  </si>
+  <si>
+    <t>Rice Crunch 8 (M-pk) [K-US]</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1197,9 +1203,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4027,7 +4030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}">
-  <dimension ref="A1:D345"/>
+  <dimension ref="A1:D347"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
@@ -8480,7 +8483,7 @@
       <c r="A306" s="4">
         <v>101070225</v>
       </c>
-      <c r="B306" s="8" t="s">
+      <c r="B306" s="5" t="s">
         <v>348</v>
       </c>
       <c r="C306" s="6" t="s">
@@ -8758,10 +8761,10 @@
     </row>
     <row r="326" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
-        <v>102002780</v>
+        <v>102002776</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="C326" s="5" t="s">
         <v>71</v>
@@ -8772,10 +8775,10 @@
     </row>
     <row r="327" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
-        <v>102002784</v>
+        <v>102002777</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C327" s="5" t="s">
         <v>71</v>
@@ -8786,10 +8789,10 @@
     </row>
     <row r="328" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
-        <v>102002785</v>
+        <v>102002780</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C328" s="5" t="s">
         <v>71</v>
@@ -8800,10 +8803,10 @@
     </row>
     <row r="329" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
-        <v>102070016</v>
+        <v>102002784</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C329" s="5" t="s">
         <v>71</v>
@@ -8814,10 +8817,10 @@
     </row>
     <row r="330" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
-        <v>102070020</v>
+        <v>102002785</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C330" s="5" t="s">
         <v>71</v>
@@ -8828,12 +8831,12 @@
     </row>
     <row r="331" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A331" s="4">
-        <v>102070038</v>
+        <v>102070016</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C331" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C331" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D331" t="s">
@@ -8842,10 +8845,10 @@
     </row>
     <row r="332" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>102070041</v>
+        <v>102070020</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="C332" s="5" t="s">
         <v>71</v>
@@ -8856,10 +8859,10 @@
     </row>
     <row r="333" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A333" s="4">
-        <v>102070042</v>
+        <v>102070038</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C333" s="6" t="s">
         <v>71</v>
@@ -8870,10 +8873,10 @@
     </row>
     <row r="334" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4">
-        <v>102070043</v>
+        <v>102070041</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C334" s="5" t="s">
         <v>71</v>
@@ -8884,12 +8887,12 @@
     </row>
     <row r="335" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A335" s="4">
-        <v>901001521</v>
+        <v>102070042</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C335" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C335" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D335" t="s">
@@ -8898,10 +8901,10 @@
     </row>
     <row r="336" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4">
-        <v>901001941</v>
+        <v>102070043</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C336" s="5" t="s">
         <v>71</v>
@@ -8912,10 +8915,10 @@
     </row>
     <row r="337" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A337" s="4">
-        <v>901001955</v>
+        <v>901001521</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C337" s="5" t="s">
         <v>71</v>
@@ -8926,10 +8929,10 @@
     </row>
     <row r="338" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4">
-        <v>901001956</v>
+        <v>901001941</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C338" s="5" t="s">
         <v>71</v>
@@ -8940,10 +8943,10 @@
     </row>
     <row r="339" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A339" s="4">
-        <v>901001957</v>
+        <v>901001955</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C339" s="5" t="s">
         <v>71</v>
@@ -8954,10 +8957,10 @@
     </row>
     <row r="340" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A340" s="4">
-        <v>901001961</v>
+        <v>901001956</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C340" s="5" t="s">
         <v>71</v>
@@ -8968,10 +8971,10 @@
     </row>
     <row r="341" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A341" s="4">
-        <v>901001964</v>
+        <v>901001957</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C341" s="5" t="s">
         <v>71</v>
@@ -8982,10 +8985,10 @@
     </row>
     <row r="342" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4">
-        <v>902000771</v>
+        <v>901001961</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C342" s="5" t="s">
         <v>71</v>
@@ -8996,10 +8999,10 @@
     </row>
     <row r="343" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>902070007</v>
+        <v>901001964</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C343" s="5" t="s">
         <v>71</v>
@@ -9010,10 +9013,10 @@
     </row>
     <row r="344" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A344" s="4">
-        <v>903000582</v>
+        <v>902000771</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C344" s="5" t="s">
         <v>71</v>
@@ -9022,12 +9025,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A345" s="4">
-        <v>903070001</v>
+        <v>902070007</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C345" s="5" t="s">
         <v>71</v>
@@ -9036,8 +9039,36 @@
         <v>320</v>
       </c>
     </row>
+    <row r="346" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A346" s="4">
+        <v>903000582</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D346" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A347" s="4">
+        <v>903070001</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D347" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D345" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
+  <autoFilter ref="A1:D347" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>